--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484560_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484560_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>L. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3359</v>
+        <v>1.4452</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5424</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7935</v>
+        <v>2.3429</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6211</v>
+        <v>0.9782</v>
       </c>
       <c r="H2" t="n">
-        <v>2.612</v>
+        <v>-1.0381</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.9908</v>
+        <v>2.0163</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0291</v>
+        <v>-0.1268</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9937</v>
+        <v>-1.5021</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.9646</v>
+        <v>1.3753</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.408</v>
+        <v>1.105</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3818</v>
+        <v>0.464</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0262</v>
+        <v>0.641</v>
       </c>
       <c r="P2" t="n">
-        <v>0.733</v>
+        <v>1.0995</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.4819</v>
+        <v>1.0995</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5944</v>
+        <v>-0.0094</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5528</v>
+        <v>-0.1478</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0415</v>
+        <v>0.1384</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.6127</v>
+        <v>-0.6231</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.2907</v>
+        <v>-0.6231</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. GARCIA JIMENEZ</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7803</v>
+        <v>1.3224</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5131</v>
+        <v>-0.4463</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2934</v>
+        <v>1.7687</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9782</v>
+        <v>0.6211</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0381</v>
+        <v>2.612</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0163</v>
+        <v>-1.9908</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1268</v>
+        <v>2.0291</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.5021</v>
+        <v>2.9937</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3753</v>
+        <v>-0.9646</v>
       </c>
       <c r="M3" t="n">
-        <v>1.105</v>
+        <v>-1.408</v>
       </c>
       <c r="N3" t="n">
-        <v>0.464</v>
+        <v>-0.3818</v>
       </c>
       <c r="O3" t="n">
-        <v>0.641</v>
+        <v>-1.0262</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0995</v>
+        <v>0.733</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0995</v>
+        <v>3.4819</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3256</v>
+        <v>0.5809</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2368</v>
+        <v>0.5641</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0888</v>
+        <v>0.0167</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6231</v>
+        <v>-0.6127</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6231</v>
+        <v>-0.2907</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5971</v>
+        <v>1.0367</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7597</v>
+        <v>1.1993</v>
       </c>
       <c r="F4" t="n">
         <v>-0.1626</v>
@@ -766,10 +766,10 @@
         <v>0.733</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4216</v>
+        <v>0.0181</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3122</v>
+        <v>0.1275</v>
       </c>
       <c r="U4" t="n">
         <v>-0.1094</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5592</v>
+        <v>0.246</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8728</v>
+        <v>-1.1613</v>
       </c>
       <c r="F5" t="n">
-        <v>1.432</v>
+        <v>1.4073</v>
       </c>
       <c r="G5" t="n">
         <v>0.5944</v>
@@ -844,13 +844,13 @@
         <v>1.0995</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0747</v>
+        <v>-0.2385</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2187</v>
+        <v>-0.0697</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.144</v>
+        <v>-0.1687</v>
       </c>
       <c r="V5" t="n">
         <v>0.6231</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. TALLON GUIA</t>
+          <t>J. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3335</v>
+        <v>0.0448</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8062</v>
+        <v>0.3339</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4727</v>
+        <v>-0.2891</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3846</v>
+        <v>-0.099</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2564</v>
+        <v>-0.7531</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.641</v>
+        <v>0.6541</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.641</v>
+        <v>0.1423</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.576</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.641</v>
+        <v>0.7183</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2564</v>
+        <v>-0.2413</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2564</v>
+        <v>-0.1771</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.0643</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1833</v>
+        <v>0.733</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1833</v>
+        <v>0.733</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1321</v>
+        <v>0.0547</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1652</v>
+        <v>0.1916</v>
       </c>
       <c r="U6" t="n">
-        <v>0.033</v>
+        <v>-0.1369</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CARRERAS GARRIGA</t>
+          <t>J. TALLON GUIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4569</v>
+        <v>-0.2289</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.075</v>
+        <v>-0.7511</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6181</v>
+        <v>0.5222</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3791</v>
+        <v>-0.3846</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0055</v>
+        <v>0.2564</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3846</v>
+        <v>-0.641</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0433</v>
+        <v>-0.641</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0433</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.641</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3357</v>
+        <v>0.2564</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0489</v>
+        <v>0.2564</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3846</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.1833</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.103</v>
+        <v>-0.0275</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2021</v>
+        <v>-0.1101</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>J. CARRERAS GARRIGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6797</v>
+        <v>-0.3083</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8431</v>
+        <v>-1.075</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5228</v>
+        <v>0.7667</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7786999999999999</v>
+        <v>0.3791</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1448</v>
+        <v>-0.0055</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9235</v>
+        <v>0.3846</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7237</v>
+        <v>0.0433</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5024</v>
+        <v>0.3357</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4122</v>
+        <v>-0.0489</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0902</v>
+        <v>0.3846</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2828</v>
+        <v>-0.733</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1991</v>
+        <v>0.1833</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6305</v>
+        <v>0.0456</v>
       </c>
       <c r="T8" t="n">
-        <v>1.316</v>
+        <v>-0.2021</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3144</v>
+        <v>0.2477</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.8142</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.2803</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MARIA VENTURA</t>
+          <t>A. BALADA SEGOVIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7358</v>
+        <v>-0.3937</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2981</v>
+        <v>-1.5121</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4377</v>
+        <v>1.1184</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.099</v>
+        <v>-1.8726</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7531</v>
+        <v>-0.1808</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6541</v>
+        <v>-1.6918</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1423</v>
+        <v>-1.0098</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.576</v>
+        <v>0.842</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7183</v>
+        <v>-1.8519</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2413</v>
+        <v>-0.8627</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1771</v>
+        <v>-1.0228</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0643</v>
+        <v>0.16</v>
       </c>
       <c r="P9" t="n">
-        <v>0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R9" t="n">
-        <v>0.733</v>
+        <v>2.0158</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7259</v>
+        <v>-0.6048</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4404</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2855</v>
+        <v>-0.0347</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6439</v>
+        <v>1.9005</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BALADA SEGOVIA</t>
+          <t>J. TORRES HERNANDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8334</v>
+        <v>-0.982</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9517</v>
+        <v>-0.6254</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1184</v>
+        <v>-0.3566</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8726</v>
+        <v>-1.8473</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1808</v>
+        <v>-0.1775</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6918</v>
+        <v>-1.6699</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0098</v>
+        <v>0.2506</v>
       </c>
       <c r="K10" t="n">
-        <v>0.842</v>
+        <v>0.6378</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8519</v>
+        <v>-0.3872</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8627</v>
+        <v>-2.0979</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0228</v>
+        <v>-0.8152</v>
       </c>
       <c r="O10" t="n">
-        <v>0.16</v>
+        <v>-1.2827</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1833</v>
+        <v>1.6493</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0158</v>
+        <v>3.4819</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0445</v>
+        <v>-0.4725</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0098</v>
+        <v>0.0012</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0347</v>
+        <v>-0.4736</v>
       </c>
       <c r="V10" t="n">
-        <v>1.9005</v>
+        <v>-0.3115</v>
       </c>
       <c r="W10" t="n">
-        <v>1.9005</v>
+        <v>0.9554</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.563</v>
+        <v>-1.3677</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.8439</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6229</v>
+        <v>-0.5238</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7467</v>
@@ -1312,13 +1312,13 @@
         <v>0.733</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2824</v>
+        <v>-0.0871</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5324</v>
+        <v>-0.4363</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2501</v>
+        <v>0.3492</v>
       </c>
       <c r="V11" t="n">
         <v>-1.267</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. TORRES HERNANDO</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0126</v>
+        <v>-1.7793</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.656</v>
+        <v>0.239</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3566</v>
+        <v>-2.0183</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8473</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1775</v>
+        <v>0.1448</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6699</v>
+        <v>-0.9235</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2506</v>
+        <v>0.7237</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6378</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3872</v>
+        <v>0.1667</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.0979</v>
+        <v>-1.5024</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8152</v>
+        <v>-0.4122</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2827</v>
+        <v>-1.0902</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R12" t="n">
-        <v>3.4819</v>
+        <v>2.1991</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.503</v>
+        <v>0.5309</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0294</v>
+        <v>0.7119</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4736</v>
+        <v>-0.181</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3115</v>
+        <v>-2.8142</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9554</v>
+        <v>-0.2803</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.267</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.5074</v>
+        <v>-10.0593</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.8354</v>
+        <v>-4.4368</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.672</v>
+        <v>-5.6224</v>
       </c>
       <c r="G13" t="n">
         <v>-4.6234</v>
@@ -1468,13 +1468,13 @@
         <v>2.3823</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5175</v>
+        <v>-0.0694</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0211</v>
+        <v>0.3775</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4964</v>
+        <v>-0.4469</v>
       </c>
       <c r="V13" t="n">
         <v>-3.1674</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.8498</v>
+        <v>-11.0241</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.8031</v>
+        <v>-9.977399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.046499999999999</v>
+        <v>-1.046600000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-7.4939</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4427000000000005</v>
+        <v>-0.4427000000000003</v>
       </c>
       <c r="I14" t="n">
         <v>-7.0512</v>
@@ -1537,7 +1537,7 @@
         <v>-4.490399999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>3.6651</v>
+        <v>3.665099999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-14.6607</v>
@@ -1546,13 +1546,13 @@
         <v>18.3256</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1048</v>
+        <v>-0.2789999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3883</v>
+        <v>0.4377</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7166999999999999</v>
+        <v>-0.7166000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-6.9162</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.3879</v>
+        <v>7.7984</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1146</v>
+        <v>4.7684</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2733</v>
+        <v>3.0299</v>
       </c>
       <c r="G15" t="n">
         <v>4.5456</v>
@@ -1624,13 +1624,13 @@
         <v>2.5656</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7952</v>
+        <v>1.2057</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3424</v>
+        <v>0.9963</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4528</v>
+        <v>0.2094</v>
       </c>
       <c r="V15" t="n">
         <v>3.1466</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3442</v>
+        <v>4.9037</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4897</v>
+        <v>2.9704</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8546</v>
+        <v>1.9332</v>
       </c>
       <c r="G16" t="n">
         <v>4.8213</v>
@@ -1702,13 +1702,13 @@
         <v>2.5656</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.4909</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1666</v>
+        <v>0.3141</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0982</v>
+        <v>0.1768</v>
       </c>
       <c r="V16" t="n">
         <v>2.5235</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3893</v>
+        <v>3.7098</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3234</v>
+        <v>2.5157</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0659</v>
+        <v>1.1941</v>
       </c>
       <c r="G17" t="n">
         <v>1.0114</v>
@@ -1780,13 +1780,13 @@
         <v>2.3823</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3839</v>
+        <v>-0.0634</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2036</v>
+        <v>-0.0113</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1803</v>
+        <v>-0.0521</v>
       </c>
       <c r="V17" t="n">
         <v>2.212</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.665</v>
+        <v>2.7831</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3519</v>
+        <v>2.8711</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6869</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>1.5827</v>
@@ -1858,13 +1858,13 @@
         <v>1.4661</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3838</v>
+        <v>-0.2656</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4012</v>
+        <v>-0.0795</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.785</v>
+        <v>-0.1861</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.373</v>
+        <v>0.7154</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0524</v>
+        <v>-0.764</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4255</v>
+        <v>1.4794</v>
       </c>
       <c r="G19" t="n">
         <v>-0.374</v>
@@ -1936,13 +1936,13 @@
         <v>0.3665</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0794</v>
+        <v>0.4218</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4955</v>
+        <v>-0.207</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5749</v>
+        <v>0.6288</v>
       </c>
       <c r="V19" t="n">
         <v>0.3011</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.334</v>
+        <v>0.4578</v>
       </c>
       <c r="E20" t="n">
         <v>-0.4597</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7936</v>
+        <v>0.9175</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4056</v>
@@ -2014,13 +2014,13 @@
         <v>1.6493</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4121</v>
+        <v>0.536</v>
       </c>
       <c r="T20" t="n">
         <v>0.4389</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0268</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3219</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2032</v>
+        <v>0.4494</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1832</v>
+        <v>-0.9909</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3865</v>
+        <v>1.4404</v>
       </c>
       <c r="G21" t="n">
         <v>0.6555</v>
@@ -2092,13 +2092,13 @@
         <v>0.3665</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0975</v>
+        <v>0.3437</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3303</v>
+        <v>-0.138</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4278</v>
+        <v>0.4817</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.209</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7113</v>
+        <v>-0.4228</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1351</v>
+        <v>0.2138</v>
       </c>
       <c r="G22" t="n">
         <v>0.4275</v>
@@ -2170,13 +2170,13 @@
         <v>1.0995</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2706</v>
+        <v>0.0965</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2941</v>
+        <v>-0.0056</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0235</v>
+        <v>0.1022</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7289</v>
+        <v>-0.5016</v>
       </c>
       <c r="E23" t="n">
         <v>-1.0839</v>
       </c>
       <c r="F23" t="n">
-        <v>0.355</v>
+        <v>0.5823</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5016</v>
@@ -2248,13 +2248,13 @@
         <v>0.1833</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4106</v>
+        <v>-0.1833</v>
       </c>
       <c r="T23" t="n">
         <v>-0.4955</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0849</v>
+        <v>0.3122</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7383999999999999</v>
+        <v>-1.0196</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9316</v>
+        <v>-1.3162</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1931</v>
+        <v>0.2966</v>
       </c>
       <c r="G24" t="n">
         <v>-0.6118</v>
@@ -2326,13 +2326,13 @@
         <v>0.1833</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.3252</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6041</v>
+        <v>0.2195</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0023</v>
+        <v>0.1058</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.2821</v>
+        <v>-1.3979</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.99</v>
+        <v>-3.3169</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7079</v>
+        <v>1.9191</v>
       </c>
       <c r="G25" t="n">
         <v>-0.4484</v>
@@ -2404,13 +2404,13 @@
         <v>1.2828</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0116</v>
+        <v>-0.1273</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.193</v>
+        <v>-0.52</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1815</v>
+        <v>0.3927</v>
       </c>
       <c r="V25" t="n">
         <v>0.6439</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.5212</v>
+        <v>-3.9166</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.8207</v>
+        <v>-3.7246</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7005</v>
+        <v>-0.192</v>
       </c>
       <c r="G26" t="n">
         <v>-2.2087</v>
@@ -2482,13 +2482,13 @@
         <v>0.5498</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3571</v>
+        <v>0.2475</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1086</v>
+        <v>0.2048</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4657</v>
+        <v>0.0428</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5889</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>11.8499</v>
+        <v>13.7729</v>
       </c>
       <c r="E27" t="n">
-        <v>1.046800000000002</v>
+        <v>1.046599999999998</v>
       </c>
       <c r="F27" t="n">
-        <v>10.8031</v>
+        <v>12.7263</v>
       </c>
       <c r="G27" t="n">
         <v>7.493900000000002</v>
@@ -2560,13 +2560,13 @@
         <v>14.6606</v>
       </c>
       <c r="S27" t="n">
-        <v>1.1045</v>
+        <v>3.0277</v>
       </c>
       <c r="T27" t="n">
-        <v>0.7166000000000001</v>
+        <v>0.7167</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3880999999999998</v>
+        <v>2.3113</v>
       </c>
       <c r="V27" t="n">
         <v>6.916299999999999</v>
